--- a/scripts/data/patentes-modelos-tn.xlsx
+++ b/scripts/data/patentes-modelos-tn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4a9dd6b2a5906c7/Documents/barbara/JULI BOXLER/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianboxler/Desktop/Trabajos Vaxler/Don Joaquin SRL/Documentos Don Joaquin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{A400922D-29B2-4B3D-8E12-6B12C37F4B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C98C8D7-7603-46CF-851B-CA7D62330593}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5C52AF-20B5-2743-BFF3-F69C37A30E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{937F2E9C-EBA1-437F-B372-D69D3A99D252}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16800" xr2:uid="{937F2E9C-EBA1-437F-B372-D69D3A99D252}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="355">
   <si>
     <t>CHOFER</t>
   </si>
@@ -1302,10 +1299,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1324,9 +1321,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1364,7 +1361,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1470,7 +1467,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1612,7 +1609,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1620,23 +1617,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6337BAD3-B032-41CE-9301-1D0B556AEA28}">
-  <dimension ref="A1:N68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" customWidth="1"/>
     <col min="7" max="7" width="21.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="10" width="17.33203125" customWidth="1"/>
     <col min="11" max="11" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1674,11 +1671,11 @@
       <c r="M1" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -1709,7 +1706,7 @@
       <c r="J2" s="25">
         <v>2023</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="27" t="s">
         <v>346</v>
       </c>
       <c r="L2" s="19" t="s">
@@ -1720,7 +1717,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1750,7 +1747,7 @@
       <c r="M3" s="24"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1780,7 +1777,7 @@
       <c r="M4" s="24"/>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1810,7 +1807,7 @@
       <c r="M5" s="24"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -1841,7 +1838,7 @@
       <c r="J6" s="25">
         <v>2021</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="27" t="s">
         <v>347</v>
       </c>
       <c r="L6" s="25">
@@ -1854,7 +1851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1884,7 +1881,7 @@
       <c r="M7" s="24"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1914,7 +1911,7 @@
       <c r="M8" s="24"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1944,7 +1941,7 @@
       <c r="M9" s="24"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -1975,7 +1972,7 @@
       <c r="J10" s="25">
         <v>2023</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="27" t="s">
         <v>348</v>
       </c>
       <c r="L10" s="25">
@@ -1988,7 +1985,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2018,7 +2015,7 @@
       <c r="M11" s="24"/>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2048,7 +2045,7 @@
       <c r="M12" s="24"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2078,7 +2075,7 @@
       <c r="M13" s="24"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2108,7 +2105,7 @@
       <c r="M14" s="24"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2138,7 +2135,7 @@
       <c r="M15" s="24"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2168,7 +2165,7 @@
       <c r="M16" s="24"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2198,7 +2195,7 @@
       <c r="M17" s="24"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2228,7 +2225,7 @@
       <c r="M18" s="24"/>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2258,7 +2255,7 @@
       <c r="M19" s="24"/>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2288,7 +2285,7 @@
       <c r="M20" s="24"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2318,7 +2315,7 @@
       <c r="M21" s="24"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
         <v>21</v>
       </c>
@@ -2349,7 +2346,7 @@
       <c r="J22" s="25">
         <v>2024</v>
       </c>
-      <c r="K22" s="28" t="s">
+      <c r="K22" s="27" t="s">
         <v>347</v>
       </c>
       <c r="L22" s="25" t="s">
@@ -2362,7 +2359,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2392,7 +2389,7 @@
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2422,7 +2419,7 @@
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2450,7 +2447,7 @@
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2480,7 +2477,7 @@
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2510,7 +2507,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2540,7 +2537,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2570,7 +2567,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2600,7 +2597,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2630,7 +2627,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2660,7 +2657,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2690,7 +2687,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2720,7 +2717,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2750,7 +2747,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2780,7 +2777,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2810,7 +2807,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2840,7 +2837,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2870,7 +2867,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="17">
         <v>39</v>
       </c>
@@ -2901,7 +2898,7 @@
       <c r="J40" s="26">
         <v>2024</v>
       </c>
-      <c r="K40" s="28" t="s">
+      <c r="K40" s="27" t="s">
         <v>349</v>
       </c>
       <c r="L40" s="26"/>
@@ -2912,7 +2909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2942,7 +2939,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2972,7 +2969,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3002,7 +2999,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="17">
         <v>43</v>
       </c>
@@ -3044,7 +3041,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="17">
         <v>44</v>
       </c>
@@ -3086,7 +3083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="17">
         <v>45</v>
       </c>
@@ -3126,7 +3123,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="17">
         <v>46</v>
       </c>
@@ -3168,7 +3165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3198,7 +3195,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3228,7 +3225,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="17">
         <v>49</v>
       </c>
@@ -3259,7 +3256,7 @@
       <c r="J50" s="26">
         <v>2025</v>
       </c>
-      <c r="K50" s="28" t="s">
+      <c r="K50" s="27" t="s">
         <v>353</v>
       </c>
       <c r="L50" s="26"/>
@@ -3270,7 +3267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3300,7 +3297,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3330,7 +3327,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="17">
         <v>52</v>
       </c>
@@ -3361,7 +3358,7 @@
       <c r="J53" s="26">
         <v>2024</v>
       </c>
-      <c r="K53" s="28" t="s">
+      <c r="K53" s="27" t="s">
         <v>354</v>
       </c>
       <c r="L53" s="26"/>
@@ -3372,7 +3369,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3400,7 +3397,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3430,7 +3427,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3460,7 +3457,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3490,7 +3487,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3520,7 +3517,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3550,7 +3547,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3580,12 +3577,14 @@
       <c r="M60" s="16"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="9" t="s">
+        <v>318</v>
+      </c>
       <c r="D61" s="6" t="s">
         <v>316</v>
       </c>
@@ -3602,7 +3601,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="7" t="s">
         <v>315</v>
@@ -3626,7 +3625,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="7" t="s">
         <v>315</v>
@@ -3650,7 +3649,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="7" t="s">
         <v>315</v>
@@ -3674,7 +3673,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="7" t="s">
         <v>315</v>
@@ -3696,7 +3695,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="7" t="s">
         <v>315</v>
@@ -3718,7 +3717,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="7" t="s">
         <v>315</v>
@@ -3740,7 +3739,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="16"/>
       <c r="B68" s="7" t="s">
         <v>315</v>
@@ -3762,6 +3761,15 @@
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
     </row>
+    <row r="69" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="C69" s="28"/>
+    </row>
+    <row r="70" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="C70" s="28"/>
+    </row>
+    <row r="71" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="C71" s="28"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
